--- a/framework-templates/registers/Risk_Assessment_Log_v2.0_Template.xlsx
+++ b/framework-templates/registers/Risk_Assessment_Log_v2.0_Template.xlsx
@@ -744,7 +744,7 @@
     <row r="11" ht="49" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>This is the Risk Register referred to in the Risk Management Framework. It records the risks your business model creates for customers, the market and the firm, how you control them, and whether they are within your risk appetite. (The anti-money laundering Business-Wide Risk Assessment is a separate workbook.)</t>
+          <t>This is the Risk Assessment Log referred to in the Risk Management Framework. It records the risks your business model creates for customers, the market and the firm, how you control them, and whether they are within your risk appetite. (The AML Business-Wide Risk Assessment is a separate register.)</t>
         </is>
       </c>
     </row>
